--- a/data/Restoration_Monitoring_Cover_TEMPLATE.xlsx
+++ b/data/Restoration_Monitoring_Cover_TEMPLATE.xlsx
@@ -5,17 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://doimspp.sharepoint.com/sites/usgs-carbonate_budget_restoration_tool/Shared Documents/Carbonate Budget Tool Collaboration/Carbonate_Budget_Tool_Code/CarbonateBudgetRestorationTool/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\__git\CBuRT\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{BDD3F7D6-829E-47F9-9487-D0AF4BDF17A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5BB6F4DC-9A01-411C-9595-5B3056FB8A09}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37457F1C-2FB4-43DE-8414-647D239E398E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{0278FB9D-D97A-43A8-AA68-A0B70EFAF30B}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{0278FB9D-D97A-43A8-AA68-A0B70EFAF30B}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="3" r:id="rId1"/>
     <sheet name="Coral Cover input" sheetId="1" r:id="rId2"/>
-    <sheet name="Taxon list" sheetId="2" r:id="rId3"/>
+    <sheet name="Taxa" sheetId="2" r:id="rId3"/>
+    <sheet name="Metadata" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="118">
   <si>
     <t>Acropora cervicornis</t>
   </si>
@@ -330,6 +331,63 @@
     </r>
   </si>
   <si>
+    <t>• Taxa can be repeated for each Unique_Site_ID</t>
+  </si>
+  <si>
+    <r>
+      <t>Step 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Input site metadata</t>
+    </r>
+  </si>
+  <si>
+    <t>• Allowable fields for Habitat within the LowerKeys, MiddleKeys, and UpperKeys Subregions include: Inshore, MidChannel, and Offshore. These designations are based on XXX; Please reference XXX if you are unsure how to classify the habitat of your site</t>
+  </si>
+  <si>
+    <t>• Allowable fields for Subregion include: DryTortugas, LowerKeys, MiddleKeys, UpperKeys, Biscayne, SoutheastFlorida; These designations are based on XXX; Please reference XXX if you are unsure where to classify your site</t>
+  </si>
+  <si>
+    <t>• Allowable fields for Habitat within the DryTortugas Subregion includes: Bank, Lagoon, and ForeReef. These designations are based on XXX; Please reference XXX if you are unsure how to classify the habitat of your site</t>
+  </si>
+  <si>
+    <t>• Habitat designations are not currently included for reefs in the Biscayne and SoutheastFlorida Subregions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• A Unique_Site_ID is required. Please try to be as descriptive as possible (e.g., LK_AwesomePatchReef_Site148_2026). More generic site names can be included in the optional field </t>
+  </si>
+  <si>
+    <t>• Latitude and Longitude for the site should be entered in decimal degrees</t>
+  </si>
+  <si>
+    <t>•  The area of the site, in m2, must be provided</t>
+  </si>
+  <si>
+    <t>POC_Name</t>
+  </si>
+  <si>
+    <t>POC_Email</t>
+  </si>
+  <si>
+    <t>•  Please provide a point of contact (POC) first and last name and email for the baseline site data so that we can contact you with questions, if necessary</t>
+  </si>
+  <si>
+    <t>Years_Post_Restoration</t>
+  </si>
+  <si>
+    <t>•  Input the monitoring timepoint in Years_Post_Restoration; months should be entered as fractional years, e.g., 3 months post outplanting = 0.25 y</t>
+  </si>
+  <si>
+    <t>Restoration Monitoring Coral Cover Data Input README:</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -347,65 +405,47 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Species names must exactly match the names listed in "Taxon list" or you will receive an error. If you copy/paste Taxon names from another data source rather than using the dropdown Taxon list, please ensure your taxon names are an exact match to those in "Taxon list"</t>
+      <t>Species names must exactly match the names listed in the Taxoa" sheet or you will receive an error. If you copy/paste Taxon names from another data source rather than using the dropdown Taxon list, please ensure your taxon names are an exact match to those in "Taxa"</t>
     </r>
   </si>
   <si>
-    <t>• Taxa can be repeated for each Unique_Site_ID</t>
-  </si>
-  <si>
-    <r>
-      <t>Step 2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Input site metadata</t>
-    </r>
-  </si>
-  <si>
-    <t>• Allowable fields for Habitat within the LowerKeys, MiddleKeys, and UpperKeys Subregions include: Inshore, MidChannel, and Offshore. These designations are based on XXX; Please reference XXX if you are unsure how to classify the habitat of your site</t>
-  </si>
-  <si>
-    <t>• Allowable fields for Subregion include: DryTortugas, LowerKeys, MiddleKeys, UpperKeys, Biscayne, SoutheastFlorida; These designations are based on XXX; Please reference XXX if you are unsure where to classify your site</t>
-  </si>
-  <si>
-    <t>• Allowable fields for Habitat within the DryTortugas Subregion includes: Bank, Lagoon, and ForeReef. These designations are based on XXX; Please reference XXX if you are unsure how to classify the habitat of your site</t>
-  </si>
-  <si>
-    <t>• Habitat designations are not currently included for reefs in the Biscayne and SoutheastFlorida Subregions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• A Unique_Site_ID is required. Please try to be as descriptive as possible (e.g., LK_AwesomePatchReef_Site148_2026). More generic site names can be included in the optional field </t>
-  </si>
-  <si>
-    <t>• Latitude and Longitude for the site should be entered in decimal degrees</t>
-  </si>
-  <si>
-    <t>•  The area of the site, in m2, must be provided</t>
-  </si>
-  <si>
-    <t>POC_Name</t>
-  </si>
-  <si>
-    <t>POC_Email</t>
-  </si>
-  <si>
-    <t>•  Please provide a point of contact (POC) first and last name and email for the baseline site data so that we can contact you with questions, if necessary</t>
-  </si>
-  <si>
-    <t>Years_Post_Restoration</t>
-  </si>
-  <si>
-    <t>•  Input the monitoring timepoint in Years_Post_Restoration; months should be entered as fractional years, e.g., 3 months post outplanting = 0.25 y</t>
-  </si>
-  <si>
-    <t>Restoration Monitoring Coral Cover Data Input README:</t>
+    <t>DryTortugas</t>
+  </si>
+  <si>
+    <t>LowerKeys</t>
+  </si>
+  <si>
+    <t>MiddleKeys</t>
+  </si>
+  <si>
+    <t>UpperKeys</t>
+  </si>
+  <si>
+    <t>Biscayne</t>
+  </si>
+  <si>
+    <t>SoutheastFlorida</t>
+  </si>
+  <si>
+    <t>Inshore</t>
+  </si>
+  <si>
+    <t>MidChannel</t>
+  </si>
+  <si>
+    <t>Offshore</t>
+  </si>
+  <si>
+    <t>Bank</t>
+  </si>
+  <si>
+    <t>Lagoon</t>
+  </si>
+  <si>
+    <t>ForeReef</t>
+  </si>
+  <si>
+    <t>Habitat_FK</t>
   </si>
 </sst>
 </file>
@@ -513,10 +553,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -844,7 +880,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.45">
@@ -854,12 +890,12 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.45">
@@ -867,52 +903,52 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -922,75 +958,110 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA43B8BD-ADC3-43CF-846A-549918345397}">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:U79"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="3" width="13.73046875" customWidth="1"/>
-    <col min="4" max="4" width="14.19921875" customWidth="1"/>
-    <col min="5" max="5" width="13.59765625" customWidth="1"/>
-    <col min="6" max="6" width="10.265625" customWidth="1"/>
-    <col min="7" max="7" width="9.46484375" customWidth="1"/>
-    <col min="8" max="8" width="10.265625" customWidth="1"/>
-    <col min="9" max="9" width="14.06640625" customWidth="1"/>
+    <col min="1" max="1" width="12.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.46484375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.59765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.53125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.06640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1" t="s">
+        <v>99</v>
+      </c>
+      <c r="J1" t="s">
+        <v>101</v>
+      </c>
+      <c r="K1" t="s">
         <v>62</v>
       </c>
-      <c r="B1" t="s">
+      <c r="L1" t="s">
         <v>84</v>
       </c>
-      <c r="C1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G1" t="s">
-        <v>79</v>
-      </c>
-      <c r="H1" t="s">
-        <v>80</v>
-      </c>
-      <c r="I1" t="s">
-        <v>83</v>
-      </c>
-      <c r="J1" t="s">
-        <v>102</v>
-      </c>
-      <c r="K1" t="s">
-        <v>99</v>
-      </c>
-      <c r="L1" t="s">
-        <v>100</v>
-      </c>
+    </row>
+    <row r="40" spans="21:21" x14ac:dyDescent="0.45">
+      <c r="U40" s="2"/>
+    </row>
+    <row r="79" spans="21:21" x14ac:dyDescent="0.45">
+      <c r="U79" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{268EBEEC-525C-485A-BCB7-2F826408B174}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{BD8589AE-91EC-42D7-A841-164BBD4472EE}">
       <formula1>"Inshore, MidChannel, Offshore, Bank, Lagoon, ForeReef"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576" xr:uid="{2551E9F4-EAD3-4C0C-A0CF-00F9C4CBBDD7}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576" xr:uid="{909B169A-7D71-45D7-9DC3-0A60F271F7F9}">
       <formula1>"DryTortugas, LowerKeys,MiddleKeys, UpperKeys, Biscayne, SoutheastFlorida"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{101649E4-CD8D-4DAA-89FC-8D6C93B48E30}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D124A12E-A2A4-4720-9229-6043F158DB99}">
           <x14:formula1>
-            <xm:f>'Taxon list'!$A$2:$A$80</xm:f>
+            <xm:f>Taxa!$A$2:$A$80</xm:f>
           </x14:formula1>
           <xm:sqref>A2:A1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4C557318-C684-4454-90B2-DAA9C611E2F1}">
+          <x14:formula1>
+            <xm:f>Taxa!A3:A81</xm:f>
+          </x14:formula1>
+          <xm:sqref>K2:K1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{503C6635-6E0C-412E-B224-BE7F47917AFB}">
+          <x14:formula1>
+            <xm:f>Metadata!A2:A7</xm:f>
+          </x14:formula1>
+          <xm:sqref>E3:E1048576 E1</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{75D5D0E7-DCF1-499A-9DD9-50EAA3B19F46}">
+          <x14:formula1>
+            <xm:f>Metadata!B3:B9</xm:f>
+          </x14:formula1>
+          <xm:sqref>F3:F1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2BAFAA9A-DAA9-4268-8D2C-7EEDA6B86959}">
+          <x14:formula1>
+            <xm:f>Metadata!B2:B8</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1409,7 +1480,84 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E91ACD9-D362-46FE-A111-F9A1D72F71A9}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="797e7fd4-719a-42b3-b312-968ffa9058ad">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="811eef35-9bdd-441e-81aa-50455f68c6c3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -1418,7 +1566,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000AA90A7536739341825FB392424435FB" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ca57789ecb406bb7a99068f68ac4c0ed">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="797e7fd4-719a-42b3-b312-968ffa9058ad" xmlns:ns3="811eef35-9bdd-441e-81aa-50455f68c6c3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="89dc4794f4784a0bac47690674a3da53" ns2:_="" ns3:_="">
     <xsd:import namespace="797e7fd4-719a-42b3-b312-968ffa9058ad"/>
@@ -1613,18 +1761,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="797e7fd4-719a-42b3-b312-968ffa9058ad">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="811eef35-9bdd-441e-81aa-50455f68c6c3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9D3406C-31AD-4E38-96F6-B0246BC4EAE6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="797e7fd4-719a-42b3-b312-968ffa9058ad"/>
+    <ds:schemaRef ds:uri="811eef35-9bdd-441e-81aa-50455f68c6c3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D6BB395-747F-41BC-A23A-168993E4FE92}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -1632,7 +1780,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D5B4E66-2F53-40AB-B6DF-59838CE46951}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1651,17 +1799,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9D3406C-31AD-4E38-96F6-B0246BC4EAE6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="797e7fd4-719a-42b3-b312-968ffa9058ad"/>
-    <ds:schemaRef ds:uri="811eef35-9bdd-441e-81aa-50455f68c6c3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{6dd02d64-b7f3-43f7-a145-cfd68d338edf}" enabled="1" method="Standard" siteId="{0693b5ba-4b18-4d7b-9341-f32f400a5494}" removed="0"/>

--- a/data/Restoration_Monitoring_Cover_TEMPLATE.xlsx
+++ b/data/Restoration_Monitoring_Cover_TEMPLATE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\__git\CBuRT\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37457F1C-2FB4-43DE-8414-647D239E398E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63A9E8DF-63EB-463F-9D5B-D3EDE6BA8952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{0278FB9D-D97A-43A8-AA68-A0B70EFAF30B}"/>
+    <workbookView xWindow="2152" yWindow="6270" windowWidth="21600" windowHeight="11332" activeTab="1" xr2:uid="{0278FB9D-D97A-43A8-AA68-A0B70EFAF30B}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="3" r:id="rId1"/>
@@ -961,56 +961,56 @@
   <dimension ref="A1:U79"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.1328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.46484375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.59765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.53125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.3984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.06640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.06640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.53125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.59765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.46484375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E1" t="s">
         <v>78</v>
       </c>
-      <c r="B1" t="s">
+      <c r="F1" t="s">
         <v>77</v>
       </c>
-      <c r="C1" t="s">
+      <c r="G1" t="s">
         <v>79</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" t="s">
         <v>80</v>
       </c>
-      <c r="E1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>83</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>98</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>99</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>101</v>
-      </c>
-      <c r="K1" t="s">
-        <v>62</v>
-      </c>
-      <c r="L1" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="40" spans="21:21" x14ac:dyDescent="0.45">
@@ -1021,23 +1021,27 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{BD8589AE-91EC-42D7-A841-164BBD4472EE}">
-      <formula1>"Inshore, MidChannel, Offshore, Bank, Lagoon, ForeReef"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576" xr:uid="{909B169A-7D71-45D7-9DC3-0A60F271F7F9}">
-      <formula1>"DryTortugas, LowerKeys,MiddleKeys, UpperKeys, Biscayne, SoutheastFlorida"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5B2BB866-BFCE-41A4-A34A-C88A6F275E86}">
+          <x14:formula1>
+            <xm:f>Metadata!$A$2:$A$7</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E1048576</xm:sqref>
+        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D124A12E-A2A4-4720-9229-6043F158DB99}">
           <x14:formula1>
             <xm:f>Taxa!$A$2:$A$80</xm:f>
           </x14:formula1>
-          <xm:sqref>A2:A1048576</xm:sqref>
+          <xm:sqref>A4:A1048576 A1:A2</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{503C6635-6E0C-412E-B224-BE7F47917AFB}">
+          <x14:formula1>
+            <xm:f>Metadata!A2:A7</xm:f>
+          </x14:formula1>
+          <xm:sqref>C1</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4C557318-C684-4454-90B2-DAA9C611E2F1}">
           <x14:formula1>
@@ -1045,23 +1049,11 @@
           </x14:formula1>
           <xm:sqref>K2:K1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{503C6635-6E0C-412E-B224-BE7F47917AFB}">
-          <x14:formula1>
-            <xm:f>Metadata!A2:A7</xm:f>
-          </x14:formula1>
-          <xm:sqref>E3:E1048576 E1</xm:sqref>
-        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{75D5D0E7-DCF1-499A-9DD9-50EAA3B19F46}">
-          <x14:formula1>
-            <xm:f>Metadata!B3:B9</xm:f>
-          </x14:formula1>
-          <xm:sqref>F3:F1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2BAFAA9A-DAA9-4268-8D2C-7EEDA6B86959}">
           <x14:formula1>
             <xm:f>Metadata!B2:B8</xm:f>
           </x14:formula1>
-          <xm:sqref>E2</xm:sqref>
+          <xm:sqref>F2:F1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/data/Restoration_Monitoring_Cover_TEMPLATE.xlsx
+++ b/data/Restoration_Monitoring_Cover_TEMPLATE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\__git\CBuRT\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63A9E8DF-63EB-463F-9D5B-D3EDE6BA8952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB046C01-1BCD-4EF1-9E13-BECD92E81DCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2152" yWindow="6270" windowWidth="21600" windowHeight="11332" activeTab="1" xr2:uid="{0278FB9D-D97A-43A8-AA68-A0B70EFAF30B}"/>
+    <workbookView xWindow="4538" yWindow="6165" windowWidth="21599" windowHeight="11340" activeTab="1" xr2:uid="{0278FB9D-D97A-43A8-AA68-A0B70EFAF30B}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="3" r:id="rId1"/>
@@ -18,6 +18,12 @@
     <sheet name="Taxa" sheetId="2" r:id="rId3"/>
     <sheet name="Metadata" sheetId="4" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="RangeA">Metadata!$B$2:$B$4</definedName>
+    <definedName name="RangeDRTO">Metadata!$B$5:$B$7</definedName>
+    <definedName name="SEFCRI">Metadata!$B$8</definedName>
+    <definedName name="SubregionList">Metadata!$A$2:$A$5</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -42,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="119">
   <si>
     <t>Acropora cervicornis</t>
   </si>
@@ -446,6 +452,9 @@
   </si>
   <si>
     <t>Habitat_FK</t>
+  </si>
+  <si>
+    <t>SEFCRI</t>
   </si>
 </sst>
 </file>
@@ -1021,35 +1030,49 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3" xr:uid="{C07575F4-954C-4853-ACD5-09E8BF28A80F}">
+      <formula1>IF(C3="DryTortugas",        RangeDRTO,    IF(ISNUMBER(MATCH(C3, RangeA, 0)),        SubregionList,        INDIRECT("SEFCRI")) )</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{742D9482-CB78-46DF-A51D-1E40F0A43463}">
+      <formula1>IF(C2="DryTortugas",        RangeDRTO,    IF(ISNUMBER(MATCH(C2, SubregionList, 0)),        RangeA,     SEFCRI))</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5B2BB866-BFCE-41A4-A34A-C88A6F275E86}">
-          <x14:formula1>
-            <xm:f>Metadata!$A$2:$A$7</xm:f>
-          </x14:formula1>
-          <xm:sqref>E2:E1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D124A12E-A2A4-4720-9229-6043F158DB99}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{19E853D7-D267-4456-A856-63939690C631}">
           <x14:formula1>
             <xm:f>Taxa!$A$2:$A$80</xm:f>
           </x14:formula1>
           <xm:sqref>A4:A1048576 A1:A2</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{503C6635-6E0C-412E-B224-BE7F47917AFB}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{77DEFF1A-6C2D-451F-ACD1-1DB2B3FF1B4E}">
           <x14:formula1>
-            <xm:f>Metadata!A2:A7</xm:f>
+            <xm:f>Metadata!$A$2:$A$6</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{251DE18D-6D2B-4ED8-A101-F03BCA3AE48A}">
+          <x14:formula1>
+            <xm:f>Metadata!$A$2:$A$7</xm:f>
+          </x14:formula1>
+          <xm:sqref>C2:C1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B9A10017-869C-49E9-B483-32D721602470}">
+          <x14:formula1>
+            <xm:f>Metadata!A2:A6</xm:f>
           </x14:formula1>
           <xm:sqref>C1</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4C557318-C684-4454-90B2-DAA9C611E2F1}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{656BD8E1-4562-489B-8169-489916FAFC1F}">
           <x14:formula1>
             <xm:f>Taxa!A3:A81</xm:f>
           </x14:formula1>
           <xm:sqref>K2:K1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{75D5D0E7-DCF1-499A-9DD9-50EAA3B19F46}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{259403FF-0290-450E-A449-DCD86532F211}">
           <x14:formula1>
             <xm:f>Metadata!B2:B8</xm:f>
           </x14:formula1>
@@ -1474,8 +1497,11 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E91ACD9-D362-46FE-A111-F9A1D72F71A9}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="16.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
@@ -1487,7 +1513,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B2" t="s">
         <v>111</v>
@@ -1495,7 +1521,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B3" t="s">
         <v>112</v>
@@ -1503,7 +1529,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B4" t="s">
         <v>113</v>
@@ -1511,7 +1537,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B5" t="s">
         <v>114</v>
@@ -1519,7 +1545,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B6" t="s">
         <v>115</v>
@@ -1527,10 +1553,15 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B7" t="s">
         <v>116</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B8" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/data/Restoration_Monitoring_Cover_TEMPLATE.xlsx
+++ b/data/Restoration_Monitoring_Cover_TEMPLATE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\__git\CBuRT\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB046C01-1BCD-4EF1-9E13-BECD92E81DCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F4FF393-AC1E-4447-B352-89E3B33796BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4538" yWindow="6165" windowWidth="21599" windowHeight="11340" activeTab="1" xr2:uid="{0278FB9D-D97A-43A8-AA68-A0B70EFAF30B}"/>
+    <workbookView xWindow="3615" yWindow="3615" windowWidth="24495" windowHeight="10522" activeTab="1" xr2:uid="{0278FB9D-D97A-43A8-AA68-A0B70EFAF30B}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="3" r:id="rId1"/>
@@ -388,9 +388,6 @@
     <t>Years_Post_Restoration</t>
   </si>
   <si>
-    <t>•  Input the monitoring timepoint in Years_Post_Restoration; months should be entered as fractional years, e.g., 3 months post outplanting = 0.25 y</t>
-  </si>
-  <si>
     <t>Restoration Monitoring Coral Cover Data Input README:</t>
   </si>
   <si>
@@ -455,6 +452,9 @@
   </si>
   <si>
     <t>SEFCRI</t>
+  </si>
+  <si>
+    <t>•  Input the monitoring timepoint in Years_Post_Restoration; months should be entered as fractional years, e.g., 3 months post outplanting = 0.25 y; pre-restoration data should be entered as -1</t>
   </si>
 </sst>
 </file>
@@ -889,7 +889,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.45">
@@ -899,7 +899,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
@@ -952,7 +952,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.45">
@@ -970,7 +970,7 @@
   <dimension ref="A1:U79"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.6640625" customWidth="1"/>
     <col min="2" max="2" width="12.06640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.59765625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.53125" bestFit="1" customWidth="1"/>
@@ -1030,10 +1030,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3" xr:uid="{C07575F4-954C-4853-ACD5-09E8BF28A80F}">
-      <formula1>IF(C3="DryTortugas",        RangeDRTO,    IF(ISNUMBER(MATCH(C3, RangeA, 0)),        SubregionList,        INDIRECT("SEFCRI")) )</formula1>
-    </dataValidation>
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{742D9482-CB78-46DF-A51D-1E40F0A43463}">
       <formula1>IF(C2="DryTortugas",        RangeDRTO,    IF(ISNUMBER(MATCH(C2, SubregionList, 0)),        RangeA,     SEFCRI))</formula1>
     </dataValidation>
@@ -1041,42 +1038,18 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{19E853D7-D267-4456-A856-63939690C631}">
           <x14:formula1>
             <xm:f>Taxa!$A$2:$A$80</xm:f>
           </x14:formula1>
           <xm:sqref>A4:A1048576 A1:A2</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{77DEFF1A-6C2D-451F-ACD1-1DB2B3FF1B4E}">
-          <x14:formula1>
-            <xm:f>Metadata!$A$2:$A$6</xm:f>
-          </x14:formula1>
-          <xm:sqref>E2:E1048576</xm:sqref>
-        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{251DE18D-6D2B-4ED8-A101-F03BCA3AE48A}">
           <x14:formula1>
             <xm:f>Metadata!$A$2:$A$7</xm:f>
           </x14:formula1>
           <xm:sqref>C2:C1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B9A10017-869C-49E9-B483-32D721602470}">
-          <x14:formula1>
-            <xm:f>Metadata!A2:A6</xm:f>
-          </x14:formula1>
-          <xm:sqref>C1</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{656BD8E1-4562-489B-8169-489916FAFC1F}">
-          <x14:formula1>
-            <xm:f>Taxa!A3:A81</xm:f>
-          </x14:formula1>
-          <xm:sqref>K2:K1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{259403FF-0290-450E-A449-DCD86532F211}">
-          <x14:formula1>
-            <xm:f>Metadata!B2:B8</xm:f>
-          </x14:formula1>
-          <xm:sqref>F2:F1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1480,7 +1453,7 @@
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A79" s="1" t="s">
+      <c r="A79" s="2" t="s">
         <v>60</v>
       </c>
     </row>
@@ -1508,60 +1481,60 @@
         <v>81</v>
       </c>
       <c r="B1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -1590,8 +1563,8 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000AA90A7536739341825FB392424435FB" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ca57789ecb406bb7a99068f68ac4c0ed">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="797e7fd4-719a-42b3-b312-968ffa9058ad" xmlns:ns3="811eef35-9bdd-441e-81aa-50455f68c6c3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="89dc4794f4784a0bac47690674a3da53" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000AA90A7536739341825FB392424435FB" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="647735499ae6baa62e6fc7f5ed3567b4">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="797e7fd4-719a-42b3-b312-968ffa9058ad" xmlns:ns3="811eef35-9bdd-441e-81aa-50455f68c6c3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="47ff4a2bf1fedf465812d90a21a07c12" ns2:_="" ns3:_="">
     <xsd:import namespace="797e7fd4-719a-42b3-b312-968ffa9058ad"/>
     <xsd:import namespace="811eef35-9bdd-441e-81aa-50455f68c6c3"/>
     <xsd:element name="properties">
@@ -1804,7 +1777,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D5B4E66-2F53-40AB-B6DF-59838CE46951}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02F7BD48-5F3F-4E55-BF3F-9589E6E77AA5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>

--- a/data/Restoration_Monitoring_Cover_TEMPLATE.xlsx
+++ b/data/Restoration_Monitoring_Cover_TEMPLATE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\__git\CBuRT\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://doimspp.sharepoint.com/sites/usgs-carbonate_budget_restoration_tool/Shared Documents/Carbonate Budget Tool Collaboration/Carbonate_Budget_Tool_Code/CarbonateBudgetRestorationTool/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F4FF393-AC1E-4447-B352-89E3B33796BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{DB046C01-1BCD-4EF1-9E13-BECD92E81DCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1657857-4663-4D64-9142-82BF4D15F40F}"/>
   <bookViews>
-    <workbookView xWindow="3615" yWindow="3615" windowWidth="24495" windowHeight="10522" activeTab="1" xr2:uid="{0278FB9D-D97A-43A8-AA68-A0B70EFAF30B}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{0278FB9D-D97A-43A8-AA68-A0B70EFAF30B}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="3" r:id="rId1"/>
@@ -970,7 +970,7 @@
   <dimension ref="A1:U79"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.06640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.59765625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.53125" bestFit="1" customWidth="1"/>
@@ -1030,7 +1030,10 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="1">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3" xr:uid="{C07575F4-954C-4853-ACD5-09E8BF28A80F}">
+      <formula1>IF(C3="DryTortugas",        RangeDRTO,    IF(ISNUMBER(MATCH(C3, RangeA, 0)),        SubregionList,        INDIRECT("SEFCRI")) )</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{742D9482-CB78-46DF-A51D-1E40F0A43463}">
       <formula1>IF(C2="DryTortugas",        RangeDRTO,    IF(ISNUMBER(MATCH(C2, SubregionList, 0)),        RangeA,     SEFCRI))</formula1>
     </dataValidation>
@@ -1038,18 +1041,42 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{19E853D7-D267-4456-A856-63939690C631}">
           <x14:formula1>
             <xm:f>Taxa!$A$2:$A$80</xm:f>
           </x14:formula1>
           <xm:sqref>A4:A1048576 A1:A2</xm:sqref>
         </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{77DEFF1A-6C2D-451F-ACD1-1DB2B3FF1B4E}">
+          <x14:formula1>
+            <xm:f>Metadata!$A$2:$A$6</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E1048576</xm:sqref>
+        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{251DE18D-6D2B-4ED8-A101-F03BCA3AE48A}">
           <x14:formula1>
             <xm:f>Metadata!$A$2:$A$7</xm:f>
           </x14:formula1>
           <xm:sqref>C2:C1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B9A10017-869C-49E9-B483-32D721602470}">
+          <x14:formula1>
+            <xm:f>Metadata!A2:A6</xm:f>
+          </x14:formula1>
+          <xm:sqref>C1</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{656BD8E1-4562-489B-8169-489916FAFC1F}">
+          <x14:formula1>
+            <xm:f>Taxa!A3:A81</xm:f>
+          </x14:formula1>
+          <xm:sqref>K2:K1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{259403FF-0290-450E-A449-DCD86532F211}">
+          <x14:formula1>
+            <xm:f>Metadata!B2:B8</xm:f>
+          </x14:formula1>
+          <xm:sqref>F2:F1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1453,7 +1480,7 @@
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A79" s="2" t="s">
+      <c r="A79" s="1" t="s">
         <v>60</v>
       </c>
     </row>
@@ -1543,26 +1570,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="797e7fd4-719a-42b3-b312-968ffa9058ad">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="811eef35-9bdd-441e-81aa-50455f68c6c3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000AA90A7536739341825FB392424435FB" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="647735499ae6baa62e6fc7f5ed3567b4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="797e7fd4-719a-42b3-b312-968ffa9058ad" xmlns:ns3="811eef35-9bdd-441e-81aa-50455f68c6c3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="47ff4a2bf1fedf465812d90a21a07c12" ns2:_="" ns3:_="">
     <xsd:import namespace="797e7fd4-719a-42b3-b312-968ffa9058ad"/>
@@ -1757,26 +1764,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9D3406C-31AD-4E38-96F6-B0246BC4EAE6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="797e7fd4-719a-42b3-b312-968ffa9058ad"/>
-    <ds:schemaRef ds:uri="811eef35-9bdd-441e-81aa-50455f68c6c3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D6BB395-747F-41BC-A23A-168993E4FE92}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="797e7fd4-719a-42b3-b312-968ffa9058ad">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="811eef35-9bdd-441e-81aa-50455f68c6c3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02F7BD48-5F3F-4E55-BF3F-9589E6E77AA5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1795,6 +1803,25 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D6BB395-747F-41BC-A23A-168993E4FE92}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9D3406C-31AD-4E38-96F6-B0246BC4EAE6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="797e7fd4-719a-42b3-b312-968ffa9058ad"/>
+    <ds:schemaRef ds:uri="811eef35-9bdd-441e-81aa-50455f68c6c3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{6dd02d64-b7f3-43f7-a145-cfd68d338edf}" enabled="1" method="Standard" siteId="{0693b5ba-4b18-4d7b-9341-f32f400a5494}" removed="0"/>

--- a/data/Restoration_Monitoring_Cover_TEMPLATE.xlsx
+++ b/data/Restoration_Monitoring_Cover_TEMPLATE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://doimspp.sharepoint.com/sites/usgs-carbonate_budget_restoration_tool/Shared Documents/Carbonate Budget Tool Collaboration/Carbonate_Budget_Tool_Code/CarbonateBudgetRestorationTool/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\__git\CBuRT\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{DB046C01-1BCD-4EF1-9E13-BECD92E81DCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1657857-4663-4D64-9142-82BF4D15F40F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B44D822B-8680-4383-A6E0-A7A84C96E202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{0278FB9D-D97A-43A8-AA68-A0B70EFAF30B}"/>
+    <workbookView xWindow="57480" yWindow="22020" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{0278FB9D-D97A-43A8-AA68-A0B70EFAF30B}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="3" r:id="rId1"/>
@@ -970,7 +970,7 @@
   <dimension ref="A1:U79"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1328125" customWidth="1"/>
     <col min="2" max="2" width="12.06640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.59765625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.53125" bestFit="1" customWidth="1"/>
@@ -1030,10 +1030,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3" xr:uid="{C07575F4-954C-4853-ACD5-09E8BF28A80F}">
-      <formula1>IF(C3="DryTortugas",        RangeDRTO,    IF(ISNUMBER(MATCH(C3, RangeA, 0)),        SubregionList,        INDIRECT("SEFCRI")) )</formula1>
-    </dataValidation>
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{742D9482-CB78-46DF-A51D-1E40F0A43463}">
       <formula1>IF(C2="DryTortugas",        RangeDRTO,    IF(ISNUMBER(MATCH(C2, SubregionList, 0)),        RangeA,     SEFCRI))</formula1>
     </dataValidation>
@@ -1041,18 +1038,12 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{19E853D7-D267-4456-A856-63939690C631}">
           <x14:formula1>
             <xm:f>Taxa!$A$2:$A$80</xm:f>
           </x14:formula1>
           <xm:sqref>A4:A1048576 A1:A2</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{77DEFF1A-6C2D-451F-ACD1-1DB2B3FF1B4E}">
-          <x14:formula1>
-            <xm:f>Metadata!$A$2:$A$6</xm:f>
-          </x14:formula1>
-          <xm:sqref>E2:E1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{251DE18D-6D2B-4ED8-A101-F03BCA3AE48A}">
           <x14:formula1>
@@ -1065,18 +1056,6 @@
             <xm:f>Metadata!A2:A6</xm:f>
           </x14:formula1>
           <xm:sqref>C1</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{656BD8E1-4562-489B-8169-489916FAFC1F}">
-          <x14:formula1>
-            <xm:f>Taxa!A3:A81</xm:f>
-          </x14:formula1>
-          <xm:sqref>K2:K1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{259403FF-0290-450E-A449-DCD86532F211}">
-          <x14:formula1>
-            <xm:f>Metadata!B2:B8</xm:f>
-          </x14:formula1>
-          <xm:sqref>F2:F1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1570,6 +1549,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="797e7fd4-719a-42b3-b312-968ffa9058ad">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="811eef35-9bdd-441e-81aa-50455f68c6c3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000AA90A7536739341825FB392424435FB" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="647735499ae6baa62e6fc7f5ed3567b4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="797e7fd4-719a-42b3-b312-968ffa9058ad" xmlns:ns3="811eef35-9bdd-441e-81aa-50455f68c6c3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="47ff4a2bf1fedf465812d90a21a07c12" ns2:_="" ns3:_="">
     <xsd:import namespace="797e7fd4-719a-42b3-b312-968ffa9058ad"/>
@@ -1764,27 +1763,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9D3406C-31AD-4E38-96F6-B0246BC4EAE6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="797e7fd4-719a-42b3-b312-968ffa9058ad"/>
+    <ds:schemaRef ds:uri="811eef35-9bdd-441e-81aa-50455f68c6c3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="797e7fd4-719a-42b3-b312-968ffa9058ad">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="811eef35-9bdd-441e-81aa-50455f68c6c3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D6BB395-747F-41BC-A23A-168993E4FE92}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02F7BD48-5F3F-4E55-BF3F-9589E6E77AA5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1803,25 +1801,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D6BB395-747F-41BC-A23A-168993E4FE92}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9D3406C-31AD-4E38-96F6-B0246BC4EAE6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="797e7fd4-719a-42b3-b312-968ffa9058ad"/>
-    <ds:schemaRef ds:uri="811eef35-9bdd-441e-81aa-50455f68c6c3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{6dd02d64-b7f3-43f7-a145-cfd68d338edf}" enabled="1" method="Standard" siteId="{0693b5ba-4b18-4d7b-9341-f32f400a5494}" removed="0"/>
